--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.28459806409441</v>
+        <v>6.546247185415342</v>
       </c>
       <c r="D2" t="n">
-        <v>39.698421519329</v>
+        <v>6.450993496890962</v>
       </c>
       <c r="E2" t="n">
-        <v>1.783944446254547</v>
+        <v>0.289890972516364</v>
       </c>
       <c r="F2" t="n">
-        <v>1.484790435189285</v>
+        <v>0.2412784457182588</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.85563027287728</v>
+        <v>6.314039919342558</v>
       </c>
       <c r="D3" t="n">
-        <v>38.47232849109503</v>
+        <v>6.251753379802944</v>
       </c>
       <c r="E3" t="n">
-        <v>1.783944446254547</v>
+        <v>0.289890972516364</v>
       </c>
       <c r="F3" t="n">
-        <v>1.484790435189285</v>
+        <v>0.2412784457182588</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.99385937726934</v>
+        <v>5.849002148806267</v>
       </c>
       <c r="D4" t="n">
-        <v>36.12003627607496</v>
+        <v>5.86950589486218</v>
       </c>
       <c r="E4" t="n">
-        <v>1.783944446254547</v>
+        <v>0.289890972516364</v>
       </c>
       <c r="F4" t="n">
-        <v>1.484790435189285</v>
+        <v>0.2412784457182588</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
